--- a/sheet/SkillCardData.xlsx
+++ b/sheet/SkillCardData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91DF15C-416F-47A0-B21E-58C9BAF6A947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00E3E61-6716-4066-8AD7-B19F36FEC227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5595" yWindow="2910" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,10 +58,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>cost</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>督战</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -130,7 +126,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>脱壳</t>
+    <t>rank</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>空蝉</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -477,7 +477,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
@@ -494,79 +494,79 @@
     </row>
     <row r="2" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="171" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="156.75" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="114" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
@@ -577,18 +577,18 @@
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/SkillCardData.xlsx
+++ b/sheet/SkillCardData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00E3E61-6716-4066-8AD7-B19F36FEC227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCB5A28-4705-46AB-B9D4-E8780B46514A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5595" yWindow="2910" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,10 +94,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>入场时：选对侧1张点数不大于本牌的牌送墓，然后将本牌也送墓。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>死亡时：本牌点数减1，然后移动到相邻的房间。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -122,15 +118,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>入场时：选对侧1张牌移动到相邻房间。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>rank</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>空蝉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>入场时：选1张点数不大于本牌的敌对牌送墓，然后将本牌也送墓。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>入场时：选1张敌对牌移动到相邻房间。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -477,7 +477,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
@@ -494,7 +494,7 @@
     </row>
     <row r="2" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -505,13 +505,13 @@
     </row>
     <row r="3" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
@@ -555,7 +555,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
@@ -566,29 +566,29 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/SkillCardData.xlsx
+++ b/sheet/SkillCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCB5A28-4705-46AB-B9D4-E8780B46514A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9F02FC-764F-464D-8A4F-8830434B952D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -110,10 +110,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>交锋获胜时：将同一房间中玩家控制的牌送墓。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>击退</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -130,7 +126,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>入场时：选1张敌对牌移动到相邻房间。</t>
+    <t>交锋获胜时：将房间中所有玩家阵营的牌送墓。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>入场时：选房间中1张敌对牌移动到相邻房间。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -477,7 +477,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
@@ -508,7 +508,7 @@
         <v>16</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>17</v>
@@ -555,7 +555,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
@@ -566,12 +566,12 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -580,9 +580,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>2</v>

--- a/sheet/SkillCardData.xlsx
+++ b/sheet/SkillCardData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\nanDeck\DungeonCrawlDeckMaster\sheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC9F02FC-764F-464D-8A4F-8830434B952D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70B03D2-F65D-4483-9A7F-5A913DF02565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2985" yWindow="2985" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -94,10 +94,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>死亡时：本牌点数减1，然后移动到相邻的房间。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>气场</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -122,15 +118,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>入场时：选1张点数不大于本牌的敌对牌送墓，然后将本牌也送墓。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交锋获胜时：将房间中所有玩家阵营的牌送墓。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>入场时：选房间中1张敌对牌移动到相邻房间。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>交锋获胜时：消灭房间中所有玩家阵营的牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>入场时：本牌点数变为本牌所替代牌的点数，然后消灭同房间内1张点数不大于本牌的敌对牌，再消灭本牌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡时：本牌免死，然后点数减1，再移动到相邻的房间。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -477,7 +477,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
@@ -494,10 +494,10 @@
     </row>
     <row r="2" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -505,13 +505,13 @@
     </row>
     <row r="3" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="42.75" x14ac:dyDescent="0.2">
@@ -530,7 +530,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>11</v>
@@ -541,13 +541,13 @@
         <v>10</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="114" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="171" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -555,10 +555,10 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -566,29 +566,29 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="99.75" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
